--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
@@ -540,10 +540,10 @@
         <v>1469050</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0348</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>1500620</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11.6</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0347</v>
+        <v>0.1341</v>
       </c>
     </row>
     <row r="6">
@@ -584,10 +584,10 @@
         <v>1419000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11.4</v>
+        <v>3.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0353</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="7">
@@ -606,10 +606,10 @@
         <v>807400</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>11.4</v>
+        <v>3.1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0352</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="8">
@@ -628,10 +628,10 @@
         <v>5196070</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.035</v>
+        <v>0.1295</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1336969050</v>
+        <v>3483786587</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1335500000</v>
+        <v>3479958637</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1469050</v>
+        <v>3827950</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1299</v>
+        <v>0.1306</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1365700620</v>
+        <v>3389641129</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1364200000</v>
+        <v>3385916624</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1500620</v>
+        <v>3724505</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1341</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1291419000</v>
+        <v>3404231067</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1290000000</v>
+        <v>3400490531</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1419000</v>
+        <v>3740536</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1257</v>
+        <v>0.1265</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>734807400</v>
+        <v>2009822874</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>734000000</v>
+        <v>2007614500</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>807400</v>
+        <v>2208374</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1275</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>4728896070</v>
+        <v>12287481657</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>4723700000</v>
+        <v>12273980292</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5196070</v>
+        <v>13501365</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.1295</v>
+        <v>0.1317</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3483786587</v>
+        <v>3483790804</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3479958637</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3827950</v>
+        <v>3832167</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1306</v>
+        <v>0.1308</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +553,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3389641129</v>
+        <v>3389645230</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3385916624</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3724505</v>
+        <v>3728606</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>2.9</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1378</v>
+        <v>0.1379</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3404231067</v>
+        <v>3404235185</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3400490531</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3740536</v>
+        <v>3744654</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1265</v>
+        <v>0.1267</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2009822874</v>
+        <v>2009825306</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2007614500</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2208374</v>
+        <v>2210806</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1327</v>
+        <v>0.1329</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>12287481657</v>
+        <v>12287496525</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>12273980292</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13501365</v>
+        <v>13516233</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
+++ b/assets/xlsx/주별투자수익_2026-08-03_2026-08-30.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -103,11 +101,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -531,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3483790804</v>
+        <v>202824401</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3479958637</v>
+        <v>202702969</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3832167</v>
+        <v>121432</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1308</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3389645230</v>
+        <v>200513829</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3385916624</v>
+        <v>200405709</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3728606</v>
+        <v>108120</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1379</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3404235185</v>
+        <v>204072049</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3400490531</v>
+        <v>203958761</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3744654</v>
+        <v>113288</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1267</v>
+        <v>0.07389999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2009825306</v>
+        <v>114760241</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2007614500</v>
+        <v>114700927</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2210806</v>
+        <v>59314</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1329</v>
+        <v>0.0672</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>12287496525</v>
+        <v>722170520</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>12273980292</v>
+        <v>721768366</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13516233</v>
+        <v>402154</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.1318</v>
+        <v>0.0742</v>
       </c>
     </row>
   </sheetData>
